--- a/samples/sample-cafe.xlsx
+++ b/samples/sample-cafe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="146">
   <si>
     <t>標誌</t>
   </si>
@@ -413,6 +413,9 @@
     <t>說明</t>
   </si>
   <si>
+    <t>型別</t>
+  </si>
+  <si>
     <t>信任</t>
   </si>
   <si>
@@ -438,6 +441,15 @@
   </si>
   <si>
     <t>做咖啡的熟練度經驗值</t>
+  </si>
+  <si>
+    <t>新人的名字</t>
+  </si>
+  <si>
+    <t>輸入欄的標題</t>
+  </si>
+  <si>
+    <t>文字</t>
   </si>
 </sst>
 </file>
@@ -2536,10 +2548,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>129</v>
       </c>
@@ -2552,47 +2564,76 @@
       <c r="D1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/samples/sample-cafe.xlsx
+++ b/samples/sample-cafe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="147">
   <si>
     <t>標誌</t>
   </si>
@@ -299,6 +299,9 @@
     <t>新人-開心</t>
   </si>
   <si>
+    <t>中</t>
+  </si>
+  <si>
     <t>好燙[sfx=杯子]！……不過這杯好多了。</t>
   </si>
   <si>
@@ -317,12 +320,6 @@
     <t>熟客-普通</t>
   </si>
   <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>左滑入</t>
-  </si>
-  <si>
     <t>請問……今天有開嗎？</t>
   </si>
   <si>
@@ -338,7 +335,7 @@
     <t>22</t>
   </si>
   <si>
-    <t>左滑出</t>
+    <t>右滑出</t>
   </si>
   <si>
     <t>好，明天見。</t>
@@ -350,6 +347,9 @@
     <t>新人 mind</t>
   </si>
   <si>
+    <t>店長：左滑出 0.6</t>
+  </si>
+  <si>
     <t>[color=#7a6f66]（開幕之後，每天都會是這樣吧。）[/color]</t>
   </si>
   <si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>店門口-傍晚</t>
+  </si>
+  <si>
+    <t>新人：無</t>
   </si>
   <si>
     <t>傍晚，鐵捲門拉了下來。</t>
@@ -1970,7 +1973,7 @@
         <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
         <v>21</v>
@@ -1979,10 +1982,10 @@
         <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
@@ -2006,7 +2009,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2038,34 +2041,34 @@
         <v>21</v>
       </c>
       <c r="J21" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" t="s">
         <v>98</v>
-      </c>
-      <c r="K21" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>21</v>
-      </c>
-      <c r="R21" t="s">
-        <v>21</v>
-      </c>
-      <c r="S21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -2073,58 +2076,58 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
         <v>102</v>
       </c>
-      <c r="I22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" t="s">
         <v>103</v>
       </c>
-      <c r="K22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" t="s">
         <v>104</v>
-      </c>
-      <c r="M22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" t="s">
-        <v>21</v>
-      </c>
-      <c r="S22" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -2132,7 +2135,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
@@ -2156,34 +2159,34 @@
         <v>21</v>
       </c>
       <c r="J23" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
+        <v>21</v>
+      </c>
+      <c r="S23" t="s">
         <v>106</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" t="s">
-        <v>21</v>
-      </c>
-      <c r="P23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-      <c r="R23" t="s">
-        <v>21</v>
-      </c>
-      <c r="S23" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2191,58 +2194,58 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
         <v>107</v>
       </c>
-      <c r="C24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
         <v>108</v>
       </c>
-      <c r="I24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S24" t="s">
         <v>109</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" t="s">
-        <v>21</v>
-      </c>
-      <c r="S24" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -2250,25 +2253,25 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
         <v>110</v>
       </c>
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
         <v>111</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
-        <v>21</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -2380,7 +2383,7 @@
         <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>
@@ -2392,10 +2395,10 @@
         <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
@@ -2419,7 +2422,7 @@
         <v>21</v>
       </c>
       <c r="S27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -2427,7 +2430,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
@@ -2451,10 +2454,10 @@
         <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
@@ -2478,15 +2481,15 @@
         <v>21</v>
       </c>
       <c r="S28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" t="s">
         <v>128</v>
-      </c>
-      <c r="B29" t="s">
-        <v>127</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -2553,33 +2556,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -2587,16 +2590,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -2604,16 +2607,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -2621,7 +2624,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -2630,10 +2633,10 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
